--- a/graficos/NMF_mejores_diversidad.xlsx
+++ b/graficos/NMF_mejores_diversidad.xlsx
@@ -46,115 +46,115 @@
     <t>porc_del_dominio</t>
   </si>
   <si>
+    <t>comisión</t>
+  </si>
+  <si>
+    <t>antecedentes_dom</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dom_K3_1</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dom_K3_7</t>
+  </si>
+  <si>
     <t>comisión_lim</t>
   </si>
   <si>
+    <t>dictamen</t>
+  </si>
+  <si>
+    <t>comisión_lim_dictamen_K5_1</t>
+  </si>
+  <si>
+    <t>orps_lim</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dom_K3_1</t>
+  </si>
+  <si>
+    <t>orps</t>
+  </si>
+  <si>
     <t>dictamen_dom</t>
   </si>
   <si>
+    <t>orps_dictamen_dom_K3_7</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>comisión_lim_dictamen_dom_K3_5</t>
-  </si>
-  <si>
-    <t>comisión</t>
+    <t>comisión_lim_dictamen_K3_5</t>
+  </si>
+  <si>
+    <t>comisión_lim_dictamen_K4_1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dom_K3_3</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_K3_2</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen_dom</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_dom_K3_7</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_K3_1</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>comisión_dictamen_dom_K3_6</t>
+    <t>comisión_lim_dictamen_dom_K3_6</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_dictamen_K3_5</t>
+  </si>
+  <si>
+    <t>orps_lim_dictamen_dom_K3_6</t>
+  </si>
+  <si>
+    <t>todos</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K3_7</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_dom_K3_1</t>
+  </si>
+  <si>
+    <t>todos_dictamen_K3_1</t>
+  </si>
+  <si>
+    <t>orps_lim_dictamen_dom_K3_7</t>
+  </si>
+  <si>
+    <t>comisión_lim_dictamen_K4_3</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>comisión_dictamen_dom_K3_8</t>
-  </si>
-  <si>
-    <t>todos</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K3_7</t>
-  </si>
-  <si>
-    <t>orps</t>
-  </si>
-  <si>
-    <t>denuncia_dom</t>
-  </si>
-  <si>
-    <t>orps_denuncia_dom_K3_7</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K3_3</t>
-  </si>
-  <si>
-    <t>orps_lim</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen_dom</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dictamen_dom_K3_2</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K3_5</t>
-  </si>
-  <si>
-    <t>dictamen</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_K4_6</t>
-  </si>
-  <si>
-    <t>orps_lim_dictamen_dom_K3_8</t>
-  </si>
-  <si>
-    <t>orps_denuncia_dictamen_dom_K4_8</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_dom_K4_3</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_dom_K3_1</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_K3_2</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_K4_8</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_dom_K3_8</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_K3_8</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dom_K3_3</t>
-  </si>
-  <si>
-    <t>todos_dictamen_K3_5</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_K3_5</t>
+    <t>todos_antecedentes_dictamen_dom_K3_8</t>
   </si>
 </sst>
 </file>
@@ -581,21 +581,21 @@
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>-1.495637561764024</v>
+        <v>-1.650254627022796</v>
       </c>
       <c r="H2" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2">
         <v>30</v>
       </c>
       <c r="J2" s="3">
-        <v>0.2333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -604,16 +604,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="3">
         <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>-0.6917440324595875</v>
+        <v>-1.650254627022796</v>
       </c>
       <c r="H3" s="2">
         <v>8</v>
@@ -627,16 +627,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>
@@ -645,16 +645,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>-1.070388767775824</v>
+        <v>-0.6565816113986147</v>
       </c>
       <c r="H4" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I4" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J4" s="3">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -668,121 +668,121 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>-0.8435943248047378</v>
+        <v>-2.021925154730305</v>
       </c>
       <c r="H5" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2">
         <v>30</v>
       </c>
       <c r="J5" s="3">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F6" s="3">
         <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>-1.650254627022796</v>
+        <v>-1.070388767775824</v>
       </c>
       <c r="H6" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2">
         <v>30</v>
       </c>
       <c r="J6" s="3">
-        <v>0.2666666666666667</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>-0.8435943248047378</v>
+        <v>-0.3796110444575696</v>
       </c>
       <c r="H7" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2">
         <v>30</v>
       </c>
       <c r="J7" s="3">
-        <v>0.3</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>-1.190111781026169</v>
+        <v>-0.7500381334272717</v>
       </c>
       <c r="H8" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3">
-        <v>0.2666666666666667</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -796,135 +796,135 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>-0.8435943248047378</v>
+        <v>-2.011907430215903</v>
       </c>
       <c r="H9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2">
         <v>30</v>
       </c>
       <c r="J9" s="3">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
       </c>
       <c r="G10" s="3">
-        <v>-0.7391290697085839</v>
+        <v>-0.5799910747444742</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J10" s="3">
-        <v>0.025</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
       <c r="G11" s="3">
-        <v>-0.9585701477167913</v>
+        <v>-1.040721415108886</v>
       </c>
       <c r="H11" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="2">
         <v>30</v>
       </c>
       <c r="J11" s="3">
-        <v>0.2666666666666667</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
       </c>
       <c r="G12" s="3">
-        <v>-1.508529027034447</v>
+        <v>-0.3972551125688251</v>
       </c>
       <c r="H12" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I12" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J12" s="3">
-        <v>0.225</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
@@ -933,199 +933,199 @@
         <v>1</v>
       </c>
       <c r="G13" s="3">
-        <v>-1.227663972794218</v>
+        <v>-1.280723100969259</v>
       </c>
       <c r="H13" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J13" s="3">
-        <v>0.25</v>
+        <v>0.2333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F14" s="3">
         <v>1</v>
       </c>
       <c r="G14" s="3">
-        <v>-1.495637561764024</v>
+        <v>-0.3972551125688251</v>
       </c>
       <c r="H14" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14" s="2">
         <v>30</v>
       </c>
       <c r="J14" s="3">
-        <v>0.2333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
       </c>
       <c r="G15" s="3">
-        <v>-0.5799910747444742</v>
+        <v>-0.7276264214505939</v>
       </c>
       <c r="H15" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2">
         <v>30</v>
       </c>
       <c r="J15" s="3">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="3">
-        <v>-0.7440800700673026</v>
+        <v>-0.8435943248047378</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I16" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J16" s="3">
-        <v>0.025</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="3">
-        <v>-1.040721415108886</v>
+        <v>-1.650254627022796</v>
       </c>
       <c r="H17" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" s="2">
         <v>30</v>
       </c>
       <c r="J17" s="3">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
       <c r="G18" s="3">
-        <v>-0.386408802373289</v>
+        <v>-0.3973260642185674</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2">
         <v>30</v>
       </c>
       <c r="J18" s="3">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
       </c>
       <c r="G19" s="3">
-        <v>-1.650254627022796</v>
+        <v>-0.9585701477167913</v>
       </c>
       <c r="H19" s="2">
         <v>8</v>
@@ -1139,39 +1139,39 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
       </c>
       <c r="G20" s="3">
-        <v>-0.3973260642185674</v>
+        <v>-0.7500381334272717</v>
       </c>
       <c r="H20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J20" s="3">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>32</v>
@@ -1180,7 +1180,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>46</v>
@@ -1189,16 +1189,16 @@
         <v>1</v>
       </c>
       <c r="G21" s="3">
-        <v>-0.3796110444575696</v>
+        <v>-0.5436726587039878</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2">
         <v>30</v>
       </c>
       <c r="J21" s="3">
-        <v>0.03333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
   </sheetData>
